--- a/기본정보업데이트/product-upload-guide_20260416.xlsx
+++ b/기본정보업데이트/product-upload-guide_20260416.xlsx
@@ -4912,7 +4912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:T189"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
@@ -4936,7 +4936,7 @@
     <col min="20" max="20" width="9.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4998,7 +4998,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:20" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>24</v>
       </c>
